--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G5.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,43 +505,43 @@
         <v>352</v>
       </c>
       <c r="B2" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>352</v>
       </c>
       <c r="D2" t="n">
-        <v>94.10879247890132</v>
+        <v>94.26731906474527</v>
       </c>
       <c r="E2" t="n">
-        <v>507.7</v>
+        <v>526.91</v>
       </c>
       <c r="F2" t="n">
-        <v>145.0691199006044</v>
+        <v>139.7802132689394</v>
       </c>
       <c r="G2" t="n">
-        <v>3416.993644330058</v>
+        <v>2722.066530767583</v>
       </c>
       <c r="H2" t="n">
-        <v>-607.3514750394983</v>
+        <v>-409.4546604641689</v>
       </c>
       <c r="I2" t="n">
-        <v>6.125</v>
+        <v>7.015000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>23.07</v>
+        <v>31.925</v>
       </c>
       <c r="K2" t="n">
-        <v>3.615</v>
+        <v>4.574999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>5.015000000000001</v>
+        <v>6.209999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>225.657973057641</v>
+        <v>225.4732052415815</v>
       </c>
       <c r="N2" t="n">
-        <v>5.15778066693646</v>
+        <v>5.162657083137975</v>
       </c>
     </row>
     <row r="3">
@@ -549,43 +549,43 @@
         <v>352</v>
       </c>
       <c r="B3" t="n">
-        <v>142</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>352</v>
       </c>
       <c r="D3" t="n">
-        <v>94.10879247890132</v>
+        <v>94.26731906474527</v>
       </c>
       <c r="E3" t="n">
-        <v>507.7</v>
+        <v>526.91</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0691199006044</v>
+        <v>139.7802132689394</v>
       </c>
       <c r="G3" t="n">
-        <v>3416.993644330058</v>
+        <v>2722.066530767583</v>
       </c>
       <c r="H3" t="n">
-        <v>-607.3514750394983</v>
+        <v>-409.4546604641689</v>
       </c>
       <c r="I3" t="n">
-        <v>6.125</v>
+        <v>7.015000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>23.07</v>
+        <v>31.925</v>
       </c>
       <c r="K3" t="n">
-        <v>3.615</v>
+        <v>4.574999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>5.015000000000001</v>
+        <v>6.209999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>225.657973057641</v>
+        <v>225.4732052415815</v>
       </c>
       <c r="N3" t="n">
-        <v>5.15778066693646</v>
+        <v>5.162657083137975</v>
       </c>
     </row>
     <row r="4">
@@ -593,43 +593,43 @@
         <v>352</v>
       </c>
       <c r="B4" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>352</v>
       </c>
       <c r="D4" t="n">
-        <v>94.09990610388661</v>
+        <v>94.26054090221572</v>
       </c>
       <c r="E4" t="n">
-        <v>509.595</v>
+        <v>528.865</v>
       </c>
       <c r="F4" t="n">
-        <v>144.5296601684413</v>
+        <v>139.2635023560585</v>
       </c>
       <c r="G4" t="n">
-        <v>3438.380081732805</v>
+        <v>2738.493751248922</v>
       </c>
       <c r="H4" t="n">
-        <v>-600.6945780404083</v>
+        <v>-404.475327140546</v>
       </c>
       <c r="I4" t="n">
-        <v>6.205</v>
+        <v>7.16</v>
       </c>
       <c r="J4" t="n">
-        <v>23.63</v>
+        <v>32.86</v>
       </c>
       <c r="K4" t="n">
-        <v>3.715</v>
+        <v>4.71</v>
       </c>
       <c r="L4" t="n">
-        <v>5.145</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>225.6482751433331</v>
+        <v>225.4707372603033</v>
       </c>
       <c r="N4" t="n">
-        <v>5.15849600975352</v>
+        <v>5.163974333602314</v>
       </c>
     </row>
     <row r="5">
@@ -637,43 +637,43 @@
         <v>352</v>
       </c>
       <c r="B5" t="n">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>352</v>
       </c>
       <c r="D5" t="n">
-        <v>94.09990610388661</v>
+        <v>94.26054090221572</v>
       </c>
       <c r="E5" t="n">
-        <v>509.595</v>
+        <v>528.865</v>
       </c>
       <c r="F5" t="n">
-        <v>144.5296601684413</v>
+        <v>139.2635023560585</v>
       </c>
       <c r="G5" t="n">
-        <v>3438.380081732805</v>
+        <v>2738.493751248922</v>
       </c>
       <c r="H5" t="n">
-        <v>-600.6945780404083</v>
+        <v>-404.475327140546</v>
       </c>
       <c r="I5" t="n">
-        <v>6.205</v>
+        <v>7.16</v>
       </c>
       <c r="J5" t="n">
-        <v>23.63</v>
+        <v>32.86</v>
       </c>
       <c r="K5" t="n">
-        <v>3.715</v>
+        <v>4.71</v>
       </c>
       <c r="L5" t="n">
-        <v>5.145</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>225.6482751433331</v>
+        <v>225.4707372603033</v>
       </c>
       <c r="N5" t="n">
-        <v>5.15849600975352</v>
+        <v>5.163974333602314</v>
       </c>
     </row>
     <row r="6">
@@ -681,43 +681,43 @@
         <v>352</v>
       </c>
       <c r="B6" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>352</v>
       </c>
       <c r="D6" t="n">
-        <v>94.08995949812969</v>
+        <v>94.24889289553219</v>
       </c>
       <c r="E6" t="n">
-        <v>512.485</v>
+        <v>531.885</v>
       </c>
       <c r="F6" t="n">
-        <v>143.7146300350973</v>
+        <v>138.47277545623</v>
       </c>
       <c r="G6" t="n">
-        <v>3466.355251007948</v>
+        <v>2766.105425856737</v>
       </c>
       <c r="H6" t="n">
-        <v>-597.3041552616934</v>
+        <v>-395.3005168036569</v>
       </c>
       <c r="I6" t="n">
-        <v>6.255</v>
+        <v>7.3</v>
       </c>
       <c r="J6" t="n">
-        <v>22.44</v>
+        <v>33.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.52</v>
+        <v>4.840000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>4.960000000000001</v>
+        <v>6.575000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>225.6719931441504</v>
+        <v>225.4690776723965</v>
       </c>
       <c r="N6" t="n">
-        <v>5.154158664022789</v>
+        <v>5.16522316626869</v>
       </c>
     </row>
     <row r="7">
@@ -725,43 +725,43 @@
         <v>352</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>94.08995949812969</v>
+        <v>94.24889289553219</v>
       </c>
       <c r="E7" t="n">
-        <v>512.485</v>
+        <v>531.885</v>
       </c>
       <c r="F7" t="n">
-        <v>143.7146300350973</v>
+        <v>138.47277545623</v>
       </c>
       <c r="G7" t="n">
-        <v>3466.355251007948</v>
+        <v>2766.105425856737</v>
       </c>
       <c r="H7" t="n">
-        <v>-597.3041552616934</v>
+        <v>-395.3005168036569</v>
       </c>
       <c r="I7" t="n">
-        <v>6.255</v>
+        <v>7.3</v>
       </c>
       <c r="J7" t="n">
-        <v>22.44</v>
+        <v>33.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.52</v>
+        <v>4.840000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4.960000000000001</v>
+        <v>6.575000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>225.6719931441504</v>
+        <v>225.4690776723965</v>
       </c>
       <c r="N7" t="n">
-        <v>5.154158664022789</v>
+        <v>5.16522316626869</v>
       </c>
     </row>
     <row r="8">
@@ -769,43 +769,43 @@
         <v>352</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>94.06518569885561</v>
+        <v>94.24549549494873</v>
       </c>
       <c r="E8" t="n">
-        <v>517.9</v>
+        <v>533.29</v>
       </c>
       <c r="F8" t="n">
-        <v>142.2119949286288</v>
+        <v>138.1079565968551</v>
       </c>
       <c r="G8" t="n">
-        <v>3526.580361416173</v>
+        <v>2775.443724755338</v>
       </c>
       <c r="H8" t="n">
-        <v>-579.3527473916239</v>
+        <v>-393.9130512499631</v>
       </c>
       <c r="I8" t="n">
-        <v>6.48</v>
+        <v>7.445</v>
       </c>
       <c r="J8" t="n">
-        <v>24.115</v>
+        <v>34.755</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.98</v>
       </c>
       <c r="L8" t="n">
-        <v>5.325</v>
+        <v>6.76</v>
       </c>
       <c r="M8" t="n">
-        <v>225.647870471401</v>
+        <v>225.467517679611</v>
       </c>
       <c r="N8" t="n">
-        <v>5.156338897276304</v>
+        <v>5.166041346147504</v>
       </c>
     </row>
     <row r="9">
@@ -813,43 +813,43 @@
         <v>352</v>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>94.06518569885561</v>
+        <v>94.24549549494873</v>
       </c>
       <c r="E9" t="n">
-        <v>517.9</v>
+        <v>533.29</v>
       </c>
       <c r="F9" t="n">
-        <v>142.2119949286288</v>
+        <v>138.1079565968551</v>
       </c>
       <c r="G9" t="n">
-        <v>3526.580361416173</v>
+        <v>2775.443724755338</v>
       </c>
       <c r="H9" t="n">
-        <v>-579.3527473916239</v>
+        <v>-393.9130512499631</v>
       </c>
       <c r="I9" t="n">
-        <v>6.48</v>
+        <v>7.445</v>
       </c>
       <c r="J9" t="n">
-        <v>24.115</v>
+        <v>34.755</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>4.98</v>
       </c>
       <c r="L9" t="n">
-        <v>5.325</v>
+        <v>6.76</v>
       </c>
       <c r="M9" t="n">
-        <v>225.647870471401</v>
+        <v>225.467517679611</v>
       </c>
       <c r="N9" t="n">
-        <v>5.156338897276304</v>
+        <v>5.166041346147504</v>
       </c>
     </row>
     <row r="10">
@@ -857,43 +857,43 @@
         <v>352</v>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>352</v>
       </c>
       <c r="D10" t="n">
-        <v>94.08960372476547</v>
+        <v>94.25808323807701</v>
       </c>
       <c r="E10" t="n">
-        <v>512.48</v>
+        <v>528.655</v>
       </c>
       <c r="F10" t="n">
-        <v>143.7160321837669</v>
+        <v>139.318822622574</v>
       </c>
       <c r="G10" t="n">
-        <v>3466.724674474564</v>
+        <v>2741.733346725324</v>
       </c>
       <c r="H10" t="n">
-        <v>-596.5463447656517</v>
+        <v>-399.9442643074576</v>
       </c>
       <c r="I10" t="n">
-        <v>6.525</v>
+        <v>6.890000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>22.91</v>
+        <v>32.005</v>
       </c>
       <c r="K10" t="n">
-        <v>3.61</v>
+        <v>4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>5.140000000000001</v>
+        <v>6.355</v>
       </c>
       <c r="M10" t="n">
-        <v>225.6724038487482</v>
+        <v>225.4727061796857</v>
       </c>
       <c r="N10" t="n">
-        <v>5.154158664022789</v>
+        <v>5.156991401164897</v>
       </c>
     </row>
     <row r="11">
@@ -901,43 +901,43 @@
         <v>352</v>
       </c>
       <c r="B11" t="n">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>352</v>
       </c>
       <c r="D11" t="n">
-        <v>94.08960372476547</v>
+        <v>94.25808323807701</v>
       </c>
       <c r="E11" t="n">
-        <v>512.48</v>
+        <v>528.655</v>
       </c>
       <c r="F11" t="n">
-        <v>143.7160321837669</v>
+        <v>139.318822622574</v>
       </c>
       <c r="G11" t="n">
-        <v>3466.724674474564</v>
+        <v>2741.733346725324</v>
       </c>
       <c r="H11" t="n">
-        <v>-596.5463447656517</v>
+        <v>-399.9442643074576</v>
       </c>
       <c r="I11" t="n">
-        <v>6.525</v>
+        <v>6.890000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>22.91</v>
+        <v>32.005</v>
       </c>
       <c r="K11" t="n">
-        <v>3.61</v>
+        <v>4.66</v>
       </c>
       <c r="L11" t="n">
-        <v>5.140000000000001</v>
+        <v>6.355</v>
       </c>
       <c r="M11" t="n">
-        <v>225.6724038487482</v>
+        <v>225.4727061796857</v>
       </c>
       <c r="N11" t="n">
-        <v>5.154158664022789</v>
+        <v>5.156991401164897</v>
       </c>
     </row>
     <row r="12">
@@ -945,43 +945,43 @@
         <v>352</v>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>352</v>
       </c>
       <c r="D12" t="n">
-        <v>94.08510900405766</v>
+        <v>94.25467078333577</v>
       </c>
       <c r="E12" t="n">
-        <v>512.5700000000001</v>
+        <v>529.925</v>
       </c>
       <c r="F12" t="n">
-        <v>143.69079769307</v>
+        <v>138.9849359315693</v>
       </c>
       <c r="G12" t="n">
-        <v>3473.801150791409</v>
+        <v>2750.698567226415</v>
       </c>
       <c r="H12" t="n">
-        <v>-589.4195439172278</v>
+        <v>-398.1339184700439</v>
       </c>
       <c r="I12" t="n">
-        <v>6.605</v>
+        <v>7.02</v>
       </c>
       <c r="J12" t="n">
-        <v>23.47</v>
+        <v>32.93</v>
       </c>
       <c r="K12" t="n">
-        <v>3.705</v>
+        <v>4.79</v>
       </c>
       <c r="L12" t="n">
-        <v>5.265</v>
+        <v>6.535</v>
       </c>
       <c r="M12" t="n">
-        <v>225.6693801460776</v>
+        <v>225.4712891518126</v>
       </c>
       <c r="N12" t="n">
-        <v>5.155033593899832</v>
+        <v>5.158058968324974</v>
       </c>
     </row>
     <row r="13">
@@ -989,43 +989,6555 @@
         <v>352</v>
       </c>
       <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>352</v>
+      </c>
+      <c r="D13" t="n">
+        <v>94.25467078333577</v>
+      </c>
+      <c r="E13" t="n">
+        <v>529.925</v>
+      </c>
+      <c r="F13" t="n">
+        <v>138.9849359315693</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2750.698567226415</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-398.1339184700439</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.535</v>
+      </c>
+      <c r="M13" t="n">
+        <v>225.4712891518126</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.158058968324974</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>352</v>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>352</v>
+      </c>
+      <c r="D14" t="n">
+        <v>94.24537180442445</v>
+      </c>
+      <c r="E14" t="n">
+        <v>532.1900000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>138.3934162113848</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2772.133698443084</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-390.1999828939462</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="M14" t="n">
+        <v>225.4700327279505</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.158977461617291</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>352</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>352</v>
+      </c>
+      <c r="D15" t="n">
+        <v>94.24537180442445</v>
+      </c>
+      <c r="E15" t="n">
+        <v>532.1900000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>138.3934162113848</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2772.133698443084</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-390.1999828939462</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="M15" t="n">
+        <v>225.4700327279505</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.158977461617291</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>352</v>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>352</v>
+      </c>
+      <c r="D16" t="n">
+        <v>94.23753847388055</v>
+      </c>
+      <c r="E16" t="n">
+        <v>535.135</v>
+      </c>
+      <c r="F16" t="n">
+        <v>137.6317979080734</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2793.181145514232</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-386.518361170677</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="M16" t="n">
+        <v>225.4679279191476</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.15977125155068</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>352</v>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>352</v>
+      </c>
+      <c r="D17" t="n">
+        <v>94.23753847388055</v>
+      </c>
+      <c r="E17" t="n">
+        <v>535.135</v>
+      </c>
+      <c r="F17" t="n">
+        <v>137.6317979080734</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2793.181145514232</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-386.518361170677</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="M17" t="n">
+        <v>225.4679279191476</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.15977125155068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>352</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>352</v>
+      </c>
+      <c r="D18" t="n">
+        <v>94.23724343691508</v>
+      </c>
+      <c r="E18" t="n">
+        <v>536.765</v>
+      </c>
+      <c r="F18" t="n">
+        <v>137.2138499595482</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2799.127810347594</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-391.5541046284466</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.175</v>
+      </c>
+      <c r="J18" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="M18" t="n">
+        <v>225.4729533421985</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>352</v>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>352</v>
+      </c>
+      <c r="D19" t="n">
+        <v>94.23724343691508</v>
+      </c>
+      <c r="E19" t="n">
+        <v>536.765</v>
+      </c>
+      <c r="F19" t="n">
+        <v>137.2138499595482</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2799.127810347594</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-391.5541046284466</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.175</v>
+      </c>
+      <c r="J19" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="M19" t="n">
+        <v>225.4729533421985</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>352</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>352</v>
+      </c>
+      <c r="D20" t="n">
+        <v>94.22483246557428</v>
+      </c>
+      <c r="E20" t="n">
+        <v>540.045</v>
+      </c>
+      <c r="F20" t="n">
+        <v>136.3804723190417</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2828.567791594035</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-381.8000700392202</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J20" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.710000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>225.4724807877695</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>352</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>352</v>
+      </c>
+      <c r="D21" t="n">
+        <v>94.22483246557428</v>
+      </c>
+      <c r="E21" t="n">
+        <v>540.045</v>
+      </c>
+      <c r="F21" t="n">
+        <v>136.3804723190417</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2828.567791594035</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-381.8000700392202</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.710000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>225.4724807877695</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>352</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>352</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94.22322968853443</v>
+      </c>
+      <c r="E22" t="n">
+        <v>540.49</v>
+      </c>
+      <c r="F22" t="n">
+        <v>136.26818659649</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2832.171126105518</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-380.3395878724438</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.445</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="M22" t="n">
+        <v>225.4696012812934</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>352</v>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>352</v>
+      </c>
+      <c r="D23" t="n">
+        <v>94.22322968853443</v>
+      </c>
+      <c r="E23" t="n">
+        <v>540.49</v>
+      </c>
+      <c r="F23" t="n">
+        <v>136.26818659649</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2832.171126105518</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-380.3395878724438</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.445</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="M23" t="n">
+        <v>225.4696012812934</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>352</v>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>352</v>
+      </c>
+      <c r="D24" t="n">
+        <v>94.2180866588141</v>
+      </c>
+      <c r="E24" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>136.1019905267243</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2842.110234791534</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-374.0290914454183</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.155</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7.075</v>
+      </c>
+      <c r="M24" t="n">
+        <v>225.4671352567408</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>352</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>352</v>
+      </c>
+      <c r="D25" t="n">
+        <v>94.2180866588141</v>
+      </c>
+      <c r="E25" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>136.1019905267243</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2842.110234791534</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-374.0290914454183</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.155</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7.075</v>
+      </c>
+      <c r="M25" t="n">
+        <v>225.4671352567408</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>352</v>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>352</v>
+      </c>
+      <c r="D26" t="n">
+        <v>94.23563096850195</v>
+      </c>
+      <c r="E26" t="n">
+        <v>537.135</v>
+      </c>
+      <c r="F26" t="n">
+        <v>137.1193315898924</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2802.593009031325</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-389.9254203622322</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>32.965</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>225.4744439585889</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>352</v>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>352</v>
+      </c>
+      <c r="D27" t="n">
+        <v>94.23563096850195</v>
+      </c>
+      <c r="E27" t="n">
+        <v>537.135</v>
+      </c>
+      <c r="F27" t="n">
+        <v>137.1193315898924</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2802.593009031325</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-389.9254203622322</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J27" t="n">
+        <v>32.965</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>225.4744439585889</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>352</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>352</v>
+      </c>
+      <c r="D28" t="n">
+        <v>94.2258589993159</v>
+      </c>
+      <c r="E28" t="n">
+        <v>540.02</v>
+      </c>
+      <c r="F28" t="n">
+        <v>136.3867859959573</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2826.612743976634</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-383.0882001142509</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="J28" t="n">
+        <v>33.895</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.965000000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6.880000000000001</v>
+      </c>
+      <c r="M28" t="n">
+        <v>225.4718670079811</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>352</v>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>352</v>
+      </c>
+      <c r="D29" t="n">
+        <v>94.2258589993159</v>
+      </c>
+      <c r="E29" t="n">
+        <v>540.02</v>
+      </c>
+      <c r="F29" t="n">
+        <v>136.3867859959573</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2826.612743976634</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-383.0882001142509</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="J29" t="n">
+        <v>33.895</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.965000000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6.880000000000001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>225.4718670079811</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>352</v>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>352</v>
+      </c>
+      <c r="D30" t="n">
+        <v>94.2201454630608</v>
+      </c>
+      <c r="E30" t="n">
+        <v>541.575</v>
+      </c>
+      <c r="F30" t="n">
+        <v>135.9951847362542</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2840.128028937003</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-378.5585163956068</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.065</v>
+      </c>
+      <c r="M30" t="n">
+        <v>225.4706889570091</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>352</v>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>352</v>
+      </c>
+      <c r="D31" t="n">
+        <v>94.2201454630608</v>
+      </c>
+      <c r="E31" t="n">
+        <v>541.575</v>
+      </c>
+      <c r="F31" t="n">
+        <v>135.9951847362542</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2840.128028937003</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-378.5585163956068</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.065</v>
+      </c>
+      <c r="M31" t="n">
+        <v>225.4706889570091</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>352</v>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="n">
+        <v>352</v>
+      </c>
+      <c r="D32" t="n">
+        <v>94.21548175861207</v>
+      </c>
+      <c r="E32" t="n">
+        <v>542.46</v>
+      </c>
+      <c r="F32" t="n">
+        <v>135.77331448132</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2850.00982169085</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-373.708696999413</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.850000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>35.765</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.234999999999999</v>
+      </c>
+      <c r="L32" t="n">
+        <v>7.244999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>225.4673068049175</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>352</v>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>352</v>
+      </c>
+      <c r="D33" t="n">
+        <v>94.21548175861207</v>
+      </c>
+      <c r="E33" t="n">
+        <v>542.46</v>
+      </c>
+      <c r="F33" t="n">
+        <v>135.77331448132</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2850.00982169085</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-373.708696999413</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.850000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35.765</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.234999999999999</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.244999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>225.4673068049175</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>352</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="n">
+        <v>352</v>
+      </c>
+      <c r="D34" t="n">
+        <v>94.23300257290936</v>
+      </c>
+      <c r="E34" t="n">
+        <v>520.075</v>
+      </c>
+      <c r="F34" t="n">
+        <v>141.6172516916538</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2884.739375065115</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-464.5409480538872</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="J34" t="n">
+        <v>28.335</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="M34" t="n">
+        <v>240.1813404628136</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.163016654126754</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>352</v>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="n">
+        <v>352</v>
+      </c>
+      <c r="D35" t="n">
+        <v>94.23300257290936</v>
+      </c>
+      <c r="E35" t="n">
+        <v>520.075</v>
+      </c>
+      <c r="F35" t="n">
+        <v>141.6172516916538</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2884.739375065115</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-464.5409480538872</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="J35" t="n">
+        <v>28.335</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>240.1813404628136</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.163016654126754</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>352</v>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>352</v>
+      </c>
+      <c r="D36" t="n">
+        <v>94.22626642107966</v>
+      </c>
+      <c r="E36" t="n">
+        <v>522.0550000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>141.0801393982183</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2901.611166407484</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-460.1452824028344</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6.765000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.305</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.855</v>
+      </c>
+      <c r="M36" t="n">
+        <v>239.9863466158202</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5.164403813042594</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>352</v>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>352</v>
+      </c>
+      <c r="D37" t="n">
+        <v>94.22626642107966</v>
+      </c>
+      <c r="E37" t="n">
+        <v>522.0550000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>141.0801393982183</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2901.611166407484</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-460.1452824028344</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.765000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.305</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.855</v>
+      </c>
+      <c r="M37" t="n">
+        <v>239.9863466158202</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5.164403813042594</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>352</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="n">
+        <v>352</v>
+      </c>
+      <c r="D38" t="n">
+        <v>94.21536310555932</v>
+      </c>
+      <c r="E38" t="n">
+        <v>524.615</v>
+      </c>
+      <c r="F38" t="n">
+        <v>140.3917009112146</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2927.124574231464</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-451.2273663010005</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="J38" t="n">
+        <v>29.965</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L38" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M38" t="n">
+        <v>239.7903425089337</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.16559744651928</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>352</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="n">
+        <v>352</v>
+      </c>
+      <c r="D39" t="n">
+        <v>94.21536310555932</v>
+      </c>
+      <c r="E39" t="n">
+        <v>524.615</v>
+      </c>
+      <c r="F39" t="n">
+        <v>140.3917009112146</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2927.124574231464</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-451.2273663010005</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6.895</v>
+      </c>
+      <c r="J39" t="n">
+        <v>29.965</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M39" t="n">
+        <v>239.7903425089337</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.16559744651928</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>352</v>
+      </c>
+      <c r="D40" t="n">
+        <v>94.2088911844602</v>
+      </c>
+      <c r="E40" t="n">
+        <v>526.495</v>
+      </c>
+      <c r="F40" t="n">
+        <v>139.8903924510904</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2943.205893188876</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-446.8762722231011</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="J40" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.555</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M40" t="n">
+        <v>239.5931734497918</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.166526801241409</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>352</v>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>352</v>
+      </c>
+      <c r="D41" t="n">
+        <v>94.2088911844602</v>
+      </c>
+      <c r="E41" t="n">
+        <v>526.495</v>
+      </c>
+      <c r="F41" t="n">
+        <v>139.8903924510904</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2943.205893188876</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-446.8762722231011</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="J41" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.555</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="M41" t="n">
+        <v>239.5931734497918</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5.166526801241409</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>352</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="n">
+        <v>352</v>
+      </c>
+      <c r="D42" t="n">
+        <v>94.22074179636287</v>
+      </c>
+      <c r="E42" t="n">
+        <v>522.13</v>
+      </c>
+      <c r="F42" t="n">
+        <v>141.0598743101083</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2910.553736315205</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-451.6275959777103</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6.575</v>
+      </c>
+      <c r="J42" t="n">
+        <v>28.485</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.265</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M42" t="n">
+        <v>225.5162406870918</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.156991401164897</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>352</v>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="n">
+        <v>352</v>
+      </c>
+      <c r="D43" t="n">
+        <v>94.22074179636287</v>
+      </c>
+      <c r="E43" t="n">
+        <v>522.13</v>
+      </c>
+      <c r="F43" t="n">
+        <v>141.0598743101083</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2910.553736315205</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-451.6275959777103</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6.575</v>
+      </c>
+      <c r="J43" t="n">
+        <v>28.485</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.265</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="M43" t="n">
+        <v>225.5162406870918</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.156991401164897</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>352</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="n">
+        <v>352</v>
+      </c>
+      <c r="D44" t="n">
+        <v>94.21446285157464</v>
+      </c>
+      <c r="E44" t="n">
+        <v>523.595</v>
+      </c>
+      <c r="F44" t="n">
+        <v>140.6651938493241</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2925.107546134362</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-446.3528901814514</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J44" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6.005</v>
+      </c>
+      <c r="M44" t="n">
+        <v>225.513794754391</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.158058968324974</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>352</v>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="n">
+        <v>352</v>
+      </c>
+      <c r="D45" t="n">
+        <v>94.21446285157464</v>
+      </c>
+      <c r="E45" t="n">
+        <v>523.595</v>
+      </c>
+      <c r="F45" t="n">
+        <v>140.6651938493241</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2925.107546134362</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-446.3528901814514</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J45" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.005</v>
+      </c>
+      <c r="M45" t="n">
+        <v>225.513794754391</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5.158058968324974</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>352</v>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="n">
+        <v>352</v>
+      </c>
+      <c r="D46" t="n">
+        <v>94.20813789608164</v>
+      </c>
+      <c r="E46" t="n">
+        <v>525.485</v>
+      </c>
+      <c r="F46" t="n">
+        <v>140.1592665319407</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2940.838484028242</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-442.1140488473685</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J46" t="n">
+        <v>30.065</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6.175</v>
+      </c>
+      <c r="M46" t="n">
+        <v>225.5100462453885</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>352</v>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="n">
+        <v>352</v>
+      </c>
+      <c r="D47" t="n">
+        <v>94.20813789608164</v>
+      </c>
+      <c r="E47" t="n">
+        <v>525.485</v>
+      </c>
+      <c r="F47" t="n">
+        <v>140.1592665319407</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2940.838484028242</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-442.1140488473685</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J47" t="n">
+        <v>30.065</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.175</v>
+      </c>
+      <c r="M47" t="n">
+        <v>225.5100462453885</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>352</v>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="n">
+        <v>352</v>
+      </c>
+      <c r="D48" t="n">
+        <v>94.20066135415911</v>
+      </c>
+      <c r="E48" t="n">
+        <v>527.47</v>
+      </c>
+      <c r="F48" t="n">
+        <v>139.6318125647655</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2959.081738041553</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-436.7496889372605</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6.905</v>
+      </c>
+      <c r="J48" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.640000000000001</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6.335000000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>225.5062829317538</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>352</v>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>352</v>
+      </c>
+      <c r="D49" t="n">
+        <v>94.20066135415911</v>
+      </c>
+      <c r="E49" t="n">
+        <v>527.47</v>
+      </c>
+      <c r="F49" t="n">
+        <v>139.6318125647655</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2959.081738041553</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-436.7496889372605</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6.905</v>
+      </c>
+      <c r="J49" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.640000000000001</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6.335000000000001</v>
+      </c>
+      <c r="M49" t="n">
+        <v>225.5062829317538</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>352</v>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>352</v>
+      </c>
+      <c r="D50" t="n">
+        <v>94.20390862001881</v>
+      </c>
+      <c r="E50" t="n">
+        <v>527.8050000000001</v>
+      </c>
+      <c r="F50" t="n">
+        <v>139.543187680179</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2955.316645693691</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-443.2571745274129</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J50" t="n">
+        <v>28.975</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.025</v>
+      </c>
+      <c r="M50" t="n">
+        <v>225.5138018170128</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>352</v>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="n">
+        <v>352</v>
+      </c>
+      <c r="D51" t="n">
+        <v>94.20390862001881</v>
+      </c>
+      <c r="E51" t="n">
+        <v>527.8050000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>139.543187680179</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2955.316645693691</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-443.2571745274129</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J51" t="n">
+        <v>28.975</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6.025</v>
+      </c>
+      <c r="M51" t="n">
+        <v>225.5138018170128</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>352</v>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="n">
+        <v>352</v>
+      </c>
+      <c r="D52" t="n">
+        <v>94.19163798934269</v>
+      </c>
+      <c r="E52" t="n">
+        <v>531.61</v>
+      </c>
+      <c r="F52" t="n">
+        <v>138.5444069403075</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2987.164966035515</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-436.3715845183353</v>
+      </c>
+      <c r="I52" t="n">
+        <v>6.965</v>
+      </c>
+      <c r="J52" t="n">
+        <v>29.755</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.475000000000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="M52" t="n">
+        <v>225.5109557151517</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>352</v>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="n">
+        <v>352</v>
+      </c>
+      <c r="D53" t="n">
+        <v>94.19163798934269</v>
+      </c>
+      <c r="E53" t="n">
+        <v>531.61</v>
+      </c>
+      <c r="F53" t="n">
+        <v>138.5444069403075</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2987.164966035515</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-436.3715845183353</v>
+      </c>
+      <c r="I53" t="n">
+        <v>6.965</v>
+      </c>
+      <c r="J53" t="n">
+        <v>29.755</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.475000000000001</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="M53" t="n">
+        <v>225.5109557151517</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>352</v>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="n">
+        <v>352</v>
+      </c>
+      <c r="D54" t="n">
+        <v>94.19096223100142</v>
+      </c>
+      <c r="E54" t="n">
+        <v>531.46</v>
+      </c>
+      <c r="F54" t="n">
+        <v>138.5835099039192</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2987.232287112585</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-434.2980193931534</v>
+      </c>
+      <c r="I54" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="L54" t="n">
+        <v>6.350000000000001</v>
+      </c>
+      <c r="M54" t="n">
+        <v>225.5090338729505</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>352</v>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="n">
+        <v>352</v>
+      </c>
+      <c r="D55" t="n">
+        <v>94.19096223100142</v>
+      </c>
+      <c r="E55" t="n">
+        <v>531.46</v>
+      </c>
+      <c r="F55" t="n">
+        <v>138.5835099039192</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2987.232287112585</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-434.2980193931534</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="J55" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6.350000000000001</v>
+      </c>
+      <c r="M55" t="n">
+        <v>225.5090338729505</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>352</v>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="n">
+        <v>352</v>
+      </c>
+      <c r="D56" t="n">
+        <v>94.17791256094677</v>
+      </c>
+      <c r="E56" t="n">
+        <v>535.375</v>
+      </c>
+      <c r="F56" t="n">
+        <v>137.570099787134</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3020.745690935639</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-426.618263049737</v>
+      </c>
+      <c r="I56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>31.365</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.725000000000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>6.515000000000001</v>
+      </c>
+      <c r="M56" t="n">
+        <v>225.5074187947069</v>
+      </c>
+      <c r="N56" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>352</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>352</v>
+      </c>
+      <c r="D57" t="n">
+        <v>94.17791256094677</v>
+      </c>
+      <c r="E57" t="n">
+        <v>535.375</v>
+      </c>
+      <c r="F57" t="n">
+        <v>137.570099787134</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3020.745690935639</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-426.618263049737</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>31.365</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.725000000000001</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6.515000000000001</v>
+      </c>
+      <c r="M57" t="n">
+        <v>225.5074187947069</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>352</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>352</v>
+      </c>
+      <c r="D58" t="n">
+        <v>94.19739184305213</v>
+      </c>
+      <c r="E58" t="n">
+        <v>529.8050000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>139.0164158011662</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2972.191952495684</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-439.5606563222012</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J58" t="n">
+        <v>29.445</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6.200000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>225.5174368596672</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>352</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="n">
+        <v>352</v>
+      </c>
+      <c r="D59" t="n">
+        <v>94.19739184305213</v>
+      </c>
+      <c r="E59" t="n">
+        <v>529.8050000000001</v>
+      </c>
+      <c r="F59" t="n">
+        <v>139.0164158011662</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2972.191952495684</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-439.5606563222012</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J59" t="n">
+        <v>29.445</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6.200000000000001</v>
+      </c>
+      <c r="M59" t="n">
+        <v>225.5174368596672</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5.155379583777886</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>352</v>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n">
+        <v>352</v>
+      </c>
+      <c r="D60" t="n">
+        <v>94.1902324891484</v>
+      </c>
+      <c r="E60" t="n">
+        <v>531.87</v>
+      </c>
+      <c r="F60" t="n">
+        <v>138.4766807181019</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2989.940169722838</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-434.7055219377768</v>
+      </c>
+      <c r="I60" t="n">
+        <v>7.245</v>
+      </c>
+      <c r="J60" t="n">
+        <v>30.235</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.365</v>
+      </c>
+      <c r="M60" t="n">
+        <v>225.5140054909944</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>352</v>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="n">
+        <v>352</v>
+      </c>
+      <c r="D61" t="n">
+        <v>94.1902324891484</v>
+      </c>
+      <c r="E61" t="n">
+        <v>531.87</v>
+      </c>
+      <c r="F61" t="n">
+        <v>138.4766807181019</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2989.940169722838</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-434.7055219377768</v>
+      </c>
+      <c r="I61" t="n">
+        <v>7.245</v>
+      </c>
+      <c r="J61" t="n">
+        <v>30.235</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.565</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.365</v>
+      </c>
+      <c r="M61" t="n">
+        <v>225.5140054909944</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5.156335049207015</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>352</v>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="n">
+        <v>352</v>
+      </c>
+      <c r="D62" t="n">
+        <v>94.18649864954763</v>
+      </c>
+      <c r="E62" t="n">
+        <v>532.845</v>
+      </c>
+      <c r="F62" t="n">
+        <v>138.2232960308098</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2998.81952344977</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-431.7954409010418</v>
+      </c>
+      <c r="I62" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="J62" t="n">
+        <v>31.035</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="M62" t="n">
+        <v>225.5105702941493</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>352</v>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="n">
+        <v>352</v>
+      </c>
+      <c r="D63" t="n">
+        <v>94.18649864954763</v>
+      </c>
+      <c r="E63" t="n">
+        <v>532.845</v>
+      </c>
+      <c r="F63" t="n">
+        <v>138.2232960308098</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2998.81952344977</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-431.7954409010418</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="J63" t="n">
+        <v>31.035</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="M63" t="n">
+        <v>225.5105702941493</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5.15713646277115</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>352</v>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="n">
+        <v>352</v>
+      </c>
+      <c r="D64" t="n">
+        <v>94.17685450203741</v>
+      </c>
+      <c r="E64" t="n">
+        <v>535.79</v>
+      </c>
+      <c r="F64" t="n">
+        <v>137.463543876401</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3023.649605243585</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-426.1833551297185</v>
+      </c>
+      <c r="I64" t="n">
+        <v>7.475000000000001</v>
+      </c>
+      <c r="J64" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M64" t="n">
+        <v>225.5074865053409</v>
+      </c>
+      <c r="N64" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>352</v>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="n">
+        <v>352</v>
+      </c>
+      <c r="D65" t="n">
+        <v>94.17685450203741</v>
+      </c>
+      <c r="E65" t="n">
+        <v>535.79</v>
+      </c>
+      <c r="F65" t="n">
+        <v>137.463543876401</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3023.649605243585</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-426.1833551297185</v>
+      </c>
+      <c r="I65" t="n">
+        <v>7.475000000000001</v>
+      </c>
+      <c r="J65" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="L65" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="M65" t="n">
+        <v>225.5074865053409</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5.157810725136347</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>352</v>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="n">
+        <v>352</v>
+      </c>
+      <c r="D66" t="n">
+        <v>94.20480783028947</v>
+      </c>
+      <c r="E66" t="n">
+        <v>512.665</v>
+      </c>
+      <c r="F66" t="n">
+        <v>143.6641708982218</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3031.816972050492</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-523.4292350904831</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="J66" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.850000000000001</v>
+      </c>
+      <c r="L66" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M66" t="n">
+        <v>246.5949063454816</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5.16319264104895</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>352</v>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="n">
+        <v>352</v>
+      </c>
+      <c r="D67" t="n">
+        <v>94.20480783028947</v>
+      </c>
+      <c r="E67" t="n">
+        <v>512.665</v>
+      </c>
+      <c r="F67" t="n">
+        <v>143.6641708982218</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3031.816972050492</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-523.4292350904831</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6.305</v>
+      </c>
+      <c r="J67" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3.850000000000001</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M67" t="n">
+        <v>246.5949063454816</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5.16319264104895</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>352</v>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="n">
+        <v>352</v>
+      </c>
+      <c r="D68" t="n">
+        <v>94.19544670137765</v>
+      </c>
+      <c r="E68" t="n">
+        <v>514.665</v>
+      </c>
+      <c r="F68" t="n">
+        <v>143.1058886334545</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3053.495838138171</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-515.5494305606323</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J68" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.965000000000001</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5.395000000000001</v>
+      </c>
+      <c r="M68" t="n">
+        <v>246.4042247850776</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5.164714632761457</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>352</v>
+      </c>
+      <c r="B69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="n">
+        <v>352</v>
+      </c>
+      <c r="D69" t="n">
+        <v>94.19544670137765</v>
+      </c>
+      <c r="E69" t="n">
+        <v>514.665</v>
+      </c>
+      <c r="F69" t="n">
+        <v>143.1058886334545</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3053.495838138171</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-515.5494305606323</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J69" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.965000000000001</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.395000000000001</v>
+      </c>
+      <c r="M69" t="n">
+        <v>246.4042247850776</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5.164714632761457</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>352</v>
+      </c>
+      <c r="B70" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" t="n">
+        <v>352</v>
+      </c>
+      <c r="D70" t="n">
+        <v>94.18654886772896</v>
+      </c>
+      <c r="E70" t="n">
+        <v>517.365</v>
+      </c>
+      <c r="F70" t="n">
+        <v>142.3590543881725</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3077.046413325274</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-511.0190789044358</v>
+      </c>
+      <c r="I70" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="J70" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4.079999999999999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>5.549999999999999</v>
+      </c>
+      <c r="M70" t="n">
+        <v>246.2124380875328</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5.166050098881917</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>352</v>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="n">
+        <v>352</v>
+      </c>
+      <c r="D71" t="n">
+        <v>94.18654886772896</v>
+      </c>
+      <c r="E71" t="n">
+        <v>517.365</v>
+      </c>
+      <c r="F71" t="n">
+        <v>142.3590543881725</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3077.046413325274</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-511.0190789044358</v>
+      </c>
+      <c r="I71" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="J71" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4.079999999999999</v>
+      </c>
+      <c r="L71" t="n">
+        <v>5.549999999999999</v>
+      </c>
+      <c r="M71" t="n">
+        <v>246.2124380875328</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5.166050098881917</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>352</v>
+      </c>
+      <c r="B72" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" t="n">
+        <v>352</v>
+      </c>
+      <c r="D72" t="n">
+        <v>94.17743617722137</v>
+      </c>
+      <c r="E72" t="n">
+        <v>519.535</v>
+      </c>
+      <c r="F72" t="n">
+        <v>141.7644473876387</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3099.017320125635</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-504.220989329784</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6.675</v>
+      </c>
+      <c r="J72" t="n">
+        <v>27.735</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="M72" t="n">
+        <v>246.0195224862155</v>
+      </c>
+      <c r="N72" t="n">
+        <v>5.166946901696146</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>352</v>
+      </c>
+      <c r="B73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="n">
+        <v>352</v>
+      </c>
+      <c r="D73" t="n">
+        <v>94.17743617722137</v>
+      </c>
+      <c r="E73" t="n">
+        <v>519.535</v>
+      </c>
+      <c r="F73" t="n">
+        <v>141.7644473876387</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3099.017320125635</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-504.220989329784</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6.675</v>
+      </c>
+      <c r="J73" t="n">
+        <v>27.735</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="M73" t="n">
+        <v>246.0195224862155</v>
+      </c>
+      <c r="N73" t="n">
+        <v>5.166946901696146</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>352</v>
+      </c>
+      <c r="B74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="n">
+        <v>352</v>
+      </c>
+      <c r="D74" t="n">
+        <v>94.18708007404949</v>
+      </c>
+      <c r="E74" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>143.1517826502174</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3066.211762034597</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-501.8236047655327</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="J74" t="n">
+        <v>25.815</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M74" t="n">
+        <v>225.5639296994439</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5.156482022141813</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>352</v>
+      </c>
+      <c r="B75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="n">
+        <v>352</v>
+      </c>
+      <c r="D75" t="n">
+        <v>94.18708007404949</v>
+      </c>
+      <c r="E75" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>143.1517826502174</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3066.211762034597</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-501.8236047655327</v>
+      </c>
+      <c r="I75" t="n">
+        <v>6.345</v>
+      </c>
+      <c r="J75" t="n">
+        <v>25.815</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>225.5639296994439</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.156482022141813</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>352</v>
+      </c>
+      <c r="B76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="n">
+        <v>352</v>
+      </c>
+      <c r="D76" t="n">
+        <v>94.1838697473529</v>
+      </c>
+      <c r="E76" t="n">
+        <v>515.9300000000001</v>
+      </c>
+      <c r="F76" t="n">
+        <v>142.7550097368574</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3076.107175910638</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-501.5925000458782</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J76" t="n">
+        <v>26.495</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="L76" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="M76" t="n">
+        <v>225.5620154038406</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5.157513323931658</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>352</v>
+      </c>
+      <c r="B77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="n">
+        <v>352</v>
+      </c>
+      <c r="D77" t="n">
+        <v>94.1838697473529</v>
+      </c>
+      <c r="E77" t="n">
+        <v>515.9300000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>142.7550097368574</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3076.107175910638</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-501.5925000458782</v>
+      </c>
+      <c r="I77" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J77" t="n">
+        <v>26.495</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="M77" t="n">
+        <v>225.5620154038406</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5.157513323931658</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>352</v>
+      </c>
+      <c r="B78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="n">
+        <v>352</v>
+      </c>
+      <c r="D78" t="n">
+        <v>94.17586935861677</v>
+      </c>
+      <c r="E78" t="n">
+        <v>518.98</v>
+      </c>
+      <c r="F78" t="n">
+        <v>141.9160510492444</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3099.336956409013</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-499.5818027956963</v>
+      </c>
+      <c r="I78" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J78" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4.170000000000001</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5.720000000000001</v>
+      </c>
+      <c r="M78" t="n">
+        <v>225.5561912154241</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>352</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="n">
+        <v>352</v>
+      </c>
+      <c r="D79" t="n">
+        <v>94.17586935861677</v>
+      </c>
+      <c r="E79" t="n">
+        <v>518.98</v>
+      </c>
+      <c r="F79" t="n">
+        <v>141.9160510492444</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3099.336956409013</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-499.5818027956963</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J79" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4.170000000000001</v>
+      </c>
+      <c r="L79" t="n">
+        <v>5.720000000000001</v>
+      </c>
+      <c r="M79" t="n">
+        <v>225.5561912154241</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>352</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="n">
+        <v>352</v>
+      </c>
+      <c r="D80" t="n">
+        <v>94.16594081770937</v>
+      </c>
+      <c r="E80" t="n">
+        <v>520.97</v>
+      </c>
+      <c r="F80" t="n">
+        <v>141.3739604459698</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3121.938744383373</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-490.834091239901</v>
+      </c>
+      <c r="I80" t="n">
+        <v>6.615</v>
+      </c>
+      <c r="J80" t="n">
+        <v>27.885</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.285000000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>5.870000000000001</v>
+      </c>
+      <c r="M80" t="n">
+        <v>225.5482522666962</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>352</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="n">
+        <v>352</v>
+      </c>
+      <c r="D81" t="n">
+        <v>94.16594081770937</v>
+      </c>
+      <c r="E81" t="n">
+        <v>520.97</v>
+      </c>
+      <c r="F81" t="n">
+        <v>141.3739604459698</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3121.938744383373</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-490.834091239901</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6.615</v>
+      </c>
+      <c r="J81" t="n">
+        <v>27.885</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4.285000000000001</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5.870000000000001</v>
+      </c>
+      <c r="M81" t="n">
+        <v>225.5482522666962</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>352</v>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="n">
+        <v>352</v>
+      </c>
+      <c r="D82" t="n">
+        <v>94.16690942164902</v>
+      </c>
+      <c r="E82" t="n">
+        <v>521.795</v>
+      </c>
+      <c r="F82" t="n">
+        <v>141.150436806671</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3123.57119432456</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-495.5395867173829</v>
+      </c>
+      <c r="I82" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J82" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5.605</v>
+      </c>
+      <c r="M82" t="n">
+        <v>225.5639536075514</v>
+      </c>
+      <c r="N82" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>352</v>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="n">
+        <v>352</v>
+      </c>
+      <c r="D83" t="n">
+        <v>94.16690942164902</v>
+      </c>
+      <c r="E83" t="n">
+        <v>521.795</v>
+      </c>
+      <c r="F83" t="n">
+        <v>141.150436806671</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3123.57119432456</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-495.5395867173829</v>
+      </c>
+      <c r="I83" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="J83" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="L83" t="n">
+        <v>5.605</v>
+      </c>
+      <c r="M83" t="n">
+        <v>225.5639536075514</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>352</v>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="n">
+        <v>352</v>
+      </c>
+      <c r="D84" t="n">
+        <v>94.1568987588326</v>
+      </c>
+      <c r="E84" t="n">
+        <v>524.985</v>
+      </c>
+      <c r="F84" t="n">
+        <v>140.292755361652</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3150.415868744016</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-490.7941964044356</v>
+      </c>
+      <c r="I84" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="J84" t="n">
+        <v>26.985</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L84" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M84" t="n">
+        <v>225.5591161364715</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>352</v>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="n">
+        <v>352</v>
+      </c>
+      <c r="D85" t="n">
+        <v>94.1568987588326</v>
+      </c>
+      <c r="E85" t="n">
+        <v>524.985</v>
+      </c>
+      <c r="F85" t="n">
+        <v>140.292755361652</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3150.415868744016</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-490.7941964044356</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="J85" t="n">
+        <v>26.985</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M85" t="n">
+        <v>225.5591161364715</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>352</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="n">
+        <v>352</v>
+      </c>
+      <c r="D86" t="n">
+        <v>94.1564749562602</v>
+      </c>
+      <c r="E86" t="n">
+        <v>523.83</v>
+      </c>
+      <c r="F86" t="n">
+        <v>140.6020887950993</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3146.743694635351</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-485.7652710654801</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="J86" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4.255</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M86" t="n">
+        <v>225.5537741694696</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>352</v>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="n">
+        <v>352</v>
+      </c>
+      <c r="D87" t="n">
+        <v>94.1564749562602</v>
+      </c>
+      <c r="E87" t="n">
+        <v>523.83</v>
+      </c>
+      <c r="F87" t="n">
+        <v>140.6020887950993</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3146.743694635351</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-485.7652710654801</v>
+      </c>
+      <c r="I87" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="J87" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4.255</v>
+      </c>
+      <c r="L87" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>225.5537741694696</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>352</v>
+      </c>
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="n">
+        <v>352</v>
+      </c>
+      <c r="D88" t="n">
+        <v>94.140873690668</v>
+      </c>
+      <c r="E88" t="n">
+        <v>528.545</v>
+      </c>
+      <c r="F88" t="n">
+        <v>139.3478174489152</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3187.99683067758</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-477.7874691822734</v>
+      </c>
+      <c r="I88" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J88" t="n">
+        <v>28.365</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="L88" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="M88" t="n">
+        <v>225.5526140830324</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>352</v>
+      </c>
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="n">
+        <v>352</v>
+      </c>
+      <c r="D89" t="n">
+        <v>94.140873690668</v>
+      </c>
+      <c r="E89" t="n">
+        <v>528.545</v>
+      </c>
+      <c r="F89" t="n">
+        <v>139.3478174489152</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3187.99683067758</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-477.7874691822734</v>
+      </c>
+      <c r="I89" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J89" t="n">
+        <v>28.365</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4.365</v>
+      </c>
+      <c r="L89" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="M89" t="n">
+        <v>225.5526140830324</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>352</v>
+      </c>
+      <c r="B90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="n">
+        <v>352</v>
+      </c>
+      <c r="D90" t="n">
+        <v>94.15672498129447</v>
+      </c>
+      <c r="E90" t="n">
+        <v>524.655</v>
+      </c>
+      <c r="F90" t="n">
+        <v>140.3809973669113</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3149.746355268516</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-489.5730143807815</v>
+      </c>
+      <c r="I90" t="n">
+        <v>6.890000000000001</v>
+      </c>
+      <c r="J90" t="n">
+        <v>26.765</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4.115000000000001</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5.785000000000001</v>
+      </c>
+      <c r="M90" t="n">
+        <v>225.5648335181466</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>352</v>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="n">
+        <v>352</v>
+      </c>
+      <c r="D91" t="n">
+        <v>94.15672498129447</v>
+      </c>
+      <c r="E91" t="n">
+        <v>524.655</v>
+      </c>
+      <c r="F91" t="n">
+        <v>140.3809973669113</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3149.746355268516</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-489.5730143807815</v>
+      </c>
+      <c r="I91" t="n">
+        <v>6.890000000000001</v>
+      </c>
+      <c r="J91" t="n">
+        <v>26.765</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.115000000000001</v>
+      </c>
+      <c r="L91" t="n">
+        <v>5.785000000000001</v>
+      </c>
+      <c r="M91" t="n">
+        <v>225.5648335181466</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>352</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="n">
+        <v>352</v>
+      </c>
+      <c r="D92" t="n">
+        <v>94.15426109778932</v>
+      </c>
+      <c r="E92" t="n">
+        <v>525.04</v>
+      </c>
+      <c r="F92" t="n">
+        <v>140.2780591450878</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3154.684195176425</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-486.7287209988855</v>
+      </c>
+      <c r="I92" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J92" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4.230000000000001</v>
+      </c>
+      <c r="L92" t="n">
+        <v>5.930000000000001</v>
+      </c>
+      <c r="M92" t="n">
+        <v>225.5572749455453</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>352</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="n">
+        <v>352</v>
+      </c>
+      <c r="D93" t="n">
+        <v>94.15426109778932</v>
+      </c>
+      <c r="E93" t="n">
+        <v>525.04</v>
+      </c>
+      <c r="F93" t="n">
+        <v>140.2780591450878</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3154.684195176425</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-486.7287209988855</v>
+      </c>
+      <c r="I93" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J93" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4.230000000000001</v>
+      </c>
+      <c r="L93" t="n">
+        <v>5.930000000000001</v>
+      </c>
+      <c r="M93" t="n">
+        <v>225.5572749455453</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>352</v>
+      </c>
+      <c r="B94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="n">
+        <v>352</v>
+      </c>
+      <c r="D94" t="n">
+        <v>94.14538548437255</v>
+      </c>
+      <c r="E94" t="n">
+        <v>527.535</v>
+      </c>
+      <c r="F94" t="n">
+        <v>139.6146078905416</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3177.251206326933</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-481.2826440639636</v>
+      </c>
+      <c r="I94" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="J94" t="n">
+        <v>28.155</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4.345000000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M94" t="n">
+        <v>225.5554828828</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>352</v>
+      </c>
+      <c r="B95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="n">
+        <v>352</v>
+      </c>
+      <c r="D95" t="n">
+        <v>94.14538548437255</v>
+      </c>
+      <c r="E95" t="n">
+        <v>527.535</v>
+      </c>
+      <c r="F95" t="n">
+        <v>139.6146078905416</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3177.251206326933</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-481.2826440639636</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="J95" t="n">
+        <v>28.155</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4.345000000000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="M95" t="n">
+        <v>225.5554828828</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>352</v>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="n">
+        <v>352</v>
+      </c>
+      <c r="D96" t="n">
+        <v>94.13677344043744</v>
+      </c>
+      <c r="E96" t="n">
+        <v>529.55</v>
+      </c>
+      <c r="F96" t="n">
+        <v>139.0833578954525</v>
+      </c>
+      <c r="G96" t="n">
+        <v>3197.920745570914</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-474.7672242520549</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="J96" t="n">
+        <v>28.855</v>
+      </c>
+      <c r="K96" t="n">
+        <v>4.455</v>
+      </c>
+      <c r="L96" t="n">
+        <v>6.225000000000001</v>
+      </c>
+      <c r="M96" t="n">
+        <v>225.5489505246072</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>352</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="n">
+        <v>352</v>
+      </c>
+      <c r="D97" t="n">
+        <v>94.13677344043744</v>
+      </c>
+      <c r="E97" t="n">
+        <v>529.55</v>
+      </c>
+      <c r="F97" t="n">
+        <v>139.0833578954525</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3197.920745570914</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-474.7672242520549</v>
+      </c>
+      <c r="I97" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="J97" t="n">
+        <v>28.855</v>
+      </c>
+      <c r="K97" t="n">
+        <v>4.455</v>
+      </c>
+      <c r="L97" t="n">
+        <v>6.225000000000001</v>
+      </c>
+      <c r="M97" t="n">
+        <v>225.5489505246072</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>352</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="n">
+        <v>352</v>
+      </c>
+      <c r="D98" t="n">
+        <v>94.17544211080894</v>
+      </c>
+      <c r="E98" t="n">
+        <v>506.35</v>
+      </c>
+      <c r="F98" t="n">
+        <v>145.4558944870877</v>
+      </c>
+      <c r="G98" t="n">
+        <v>3181.304643083979</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-581.0979954370792</v>
+      </c>
+      <c r="I98" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J98" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="K98" t="n">
+        <v>3.574999999999999</v>
+      </c>
+      <c r="L98" t="n">
+        <v>4.865</v>
+      </c>
+      <c r="M98" t="n">
+        <v>252.7029807727054</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5.163219248428367</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>352</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98</v>
+      </c>
+      <c r="C99" t="n">
+        <v>352</v>
+      </c>
+      <c r="D99" t="n">
+        <v>94.17544211080894</v>
+      </c>
+      <c r="E99" t="n">
+        <v>506.35</v>
+      </c>
+      <c r="F99" t="n">
+        <v>145.4558944870877</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3181.304643083979</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-581.0979954370792</v>
+      </c>
+      <c r="I99" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J99" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3.574999999999999</v>
+      </c>
+      <c r="L99" t="n">
+        <v>4.865</v>
+      </c>
+      <c r="M99" t="n">
+        <v>252.7029807727054</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5.163219248428367</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>352</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" t="n">
+        <v>352</v>
+      </c>
+      <c r="D100" t="n">
+        <v>94.16691048833967</v>
+      </c>
+      <c r="E100" t="n">
+        <v>508.2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>144.9263915260466</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3201.520720740072</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-574.3817310123429</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6.140000000000001</v>
+      </c>
+      <c r="J100" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L100" t="n">
+        <v>5.004999999999999</v>
+      </c>
+      <c r="M100" t="n">
+        <v>252.5161432326725</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5.165000145963221</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>352</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="n">
+        <v>352</v>
+      </c>
+      <c r="D101" t="n">
+        <v>94.16691048833967</v>
+      </c>
+      <c r="E101" t="n">
+        <v>508.2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>144.9263915260466</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3201.520720740072</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-574.3817310123429</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6.140000000000001</v>
+      </c>
+      <c r="J101" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L101" t="n">
+        <v>5.004999999999999</v>
+      </c>
+      <c r="M101" t="n">
+        <v>252.5161432326725</v>
+      </c>
+      <c r="N101" t="n">
+        <v>5.165000145963221</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>352</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" t="n">
+        <v>352</v>
+      </c>
+      <c r="D102" t="n">
+        <v>94.15619062912515</v>
+      </c>
+      <c r="E102" t="n">
+        <v>511.19</v>
+      </c>
+      <c r="F102" t="n">
+        <v>144.0787029745043</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3229.646270541796</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-568.6802113055664</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6.255</v>
+      </c>
+      <c r="J102" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3.779999999999999</v>
+      </c>
+      <c r="L102" t="n">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="M102" t="n">
+        <v>252.3282480825341</v>
+      </c>
+      <c r="N102" t="n">
+        <v>5.166383753886102</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>352</v>
+      </c>
+      <c r="B103" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" t="n">
+        <v>352</v>
+      </c>
+      <c r="D103" t="n">
+        <v>94.15619062912515</v>
+      </c>
+      <c r="E103" t="n">
+        <v>511.19</v>
+      </c>
+      <c r="F103" t="n">
+        <v>144.0787029745043</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3229.646270541796</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-568.6802113055664</v>
+      </c>
+      <c r="I103" t="n">
+        <v>6.255</v>
+      </c>
+      <c r="J103" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3.779999999999999</v>
+      </c>
+      <c r="L103" t="n">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="M103" t="n">
+        <v>252.3282480825341</v>
+      </c>
+      <c r="N103" t="n">
+        <v>5.166383753886102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>352</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103</v>
+      </c>
+      <c r="C104" t="n">
+        <v>352</v>
+      </c>
+      <c r="D104" t="n">
+        <v>94.14819586677775</v>
+      </c>
+      <c r="E104" t="n">
+        <v>512.33</v>
+      </c>
+      <c r="F104" t="n">
+        <v>143.7581093700093</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3246.414693138855</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-560.2003341813935</v>
+      </c>
+      <c r="I104" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="J104" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="K104" t="n">
+        <v>3.885</v>
+      </c>
+      <c r="L104" t="n">
+        <v>5.289999999999999</v>
+      </c>
+      <c r="M104" t="n">
+        <v>252.1390921905173</v>
+      </c>
+      <c r="N104" t="n">
+        <v>5.167464102523422</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>352</v>
+      </c>
+      <c r="B105" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" t="n">
+        <v>352</v>
+      </c>
+      <c r="D105" t="n">
+        <v>94.14819586677775</v>
+      </c>
+      <c r="E105" t="n">
+        <v>512.33</v>
+      </c>
+      <c r="F105" t="n">
+        <v>143.7581093700093</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3246.414693138855</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-560.2003341813935</v>
+      </c>
+      <c r="I105" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="J105" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3.885</v>
+      </c>
+      <c r="L105" t="n">
+        <v>5.289999999999999</v>
+      </c>
+      <c r="M105" t="n">
+        <v>252.1390921905173</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5.167464102523422</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>352</v>
+      </c>
+      <c r="B106" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" t="n">
+        <v>352</v>
+      </c>
+      <c r="D106" t="n">
+        <v>94.15774195626064</v>
+      </c>
+      <c r="E106" t="n">
+        <v>509.325</v>
+      </c>
+      <c r="F106" t="n">
+        <v>144.6062772758786</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3220.404097478618</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-564.3103826484947</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6.145</v>
+      </c>
+      <c r="J106" t="n">
+        <v>23.685</v>
+      </c>
+      <c r="K106" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L106" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="M106" t="n">
+        <v>225.6161419773028</v>
+      </c>
+      <c r="N106" t="n">
+        <v>5.156482022141813</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>352</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" t="n">
+        <v>352</v>
+      </c>
+      <c r="D107" t="n">
+        <v>94.15774195626064</v>
+      </c>
+      <c r="E107" t="n">
+        <v>509.325</v>
+      </c>
+      <c r="F107" t="n">
+        <v>144.6062772758786</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3220.404097478618</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-564.3103826484947</v>
+      </c>
+      <c r="I107" t="n">
+        <v>6.145</v>
+      </c>
+      <c r="J107" t="n">
+        <v>23.685</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="M107" t="n">
+        <v>225.6161419773028</v>
+      </c>
+      <c r="N107" t="n">
+        <v>5.156482022141813</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>352</v>
+      </c>
+      <c r="B108" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" t="n">
+        <v>352</v>
+      </c>
+      <c r="D108" t="n">
+        <v>94.14523740941554</v>
+      </c>
+      <c r="E108" t="n">
+        <v>511.695</v>
+      </c>
+      <c r="F108" t="n">
+        <v>143.9365093923858</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3249.060034035989</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-553.490942252695</v>
+      </c>
+      <c r="I108" t="n">
+        <v>6.225000000000001</v>
+      </c>
+      <c r="J108" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3.765000000000001</v>
+      </c>
+      <c r="L108" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="M108" t="n">
+        <v>225.6133220588977</v>
+      </c>
+      <c r="N108" t="n">
+        <v>5.157513323931658</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>352</v>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="n">
+        <v>352</v>
+      </c>
+      <c r="D109" t="n">
+        <v>94.14523740941554</v>
+      </c>
+      <c r="E109" t="n">
+        <v>511.695</v>
+      </c>
+      <c r="F109" t="n">
+        <v>143.9365093923858</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3249.060034035989</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-553.490942252695</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6.225000000000001</v>
+      </c>
+      <c r="J109" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3.765000000000001</v>
+      </c>
+      <c r="L109" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="M109" t="n">
+        <v>225.6133220588977</v>
+      </c>
+      <c r="N109" t="n">
+        <v>5.157513323931658</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>352</v>
+      </c>
+      <c r="B110" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" t="n">
+        <v>352</v>
+      </c>
+      <c r="D110" t="n">
+        <v>94.13679437374469</v>
+      </c>
+      <c r="E110" t="n">
+        <v>513.55</v>
+      </c>
+      <c r="F110" t="n">
+        <v>143.4165946325321</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3269.229490235756</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-547.0102720542545</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="J110" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="L110" t="n">
+        <v>5.345000000000001</v>
+      </c>
+      <c r="M110" t="n">
+        <v>225.6078807566446</v>
+      </c>
+      <c r="N110" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>352</v>
+      </c>
+      <c r="B111" t="n">
+        <v>110</v>
+      </c>
+      <c r="C111" t="n">
+        <v>352</v>
+      </c>
+      <c r="D111" t="n">
+        <v>94.13679437374469</v>
+      </c>
+      <c r="E111" t="n">
+        <v>513.55</v>
+      </c>
+      <c r="F111" t="n">
+        <v>143.4165946325321</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3269.229490235756</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-547.0102720542545</v>
+      </c>
+      <c r="I111" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="J111" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="L111" t="n">
+        <v>5.345000000000001</v>
+      </c>
+      <c r="M111" t="n">
+        <v>225.6078807566446</v>
+      </c>
+      <c r="N111" t="n">
+        <v>5.158393968249352</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>352</v>
+      </c>
+      <c r="B112" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" t="n">
+        <v>352</v>
+      </c>
+      <c r="D112" t="n">
+        <v>94.13425463598642</v>
+      </c>
+      <c r="E112" t="n">
+        <v>514.5650000000001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>143.1336996755257</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3276.67145352932</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-546.4399635259315</v>
+      </c>
+      <c r="I112" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="J112" t="n">
+        <v>25.535</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L112" t="n">
+        <v>5.475000000000001</v>
+      </c>
+      <c r="M112" t="n">
+        <v>225.5993269787848</v>
+      </c>
+      <c r="N112" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>352</v>
+      </c>
+      <c r="B113" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" t="n">
+        <v>352</v>
+      </c>
+      <c r="D113" t="n">
+        <v>94.13425463598642</v>
+      </c>
+      <c r="E113" t="n">
+        <v>514.5650000000001</v>
+      </c>
+      <c r="F113" t="n">
+        <v>143.1336996755257</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3276.67145352932</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-546.4399635259315</v>
+      </c>
+      <c r="I113" t="n">
+        <v>6.390000000000001</v>
+      </c>
+      <c r="J113" t="n">
+        <v>25.535</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L113" t="n">
+        <v>5.475000000000001</v>
+      </c>
+      <c r="M113" t="n">
+        <v>225.5993269787848</v>
+      </c>
+      <c r="N113" t="n">
+        <v>5.159149137883177</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>352</v>
+      </c>
+      <c r="B114" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" t="n">
+        <v>352</v>
+      </c>
+      <c r="D114" t="n">
+        <v>94.11903869596536</v>
+      </c>
+      <c r="E114" t="n">
+        <v>518.61</v>
+      </c>
+      <c r="F114" t="n">
+        <v>142.017300425246</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3316.791856237693</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-538.5539687234498</v>
+      </c>
+      <c r="I114" t="n">
+        <v>6.425</v>
+      </c>
+      <c r="J114" t="n">
+        <v>24.175</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="L114" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M114" t="n">
+        <v>225.6160617043384</v>
+      </c>
+      <c r="N114" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>352</v>
+      </c>
+      <c r="B115" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" t="n">
+        <v>352</v>
+      </c>
+      <c r="D115" t="n">
+        <v>94.11903869596536</v>
+      </c>
+      <c r="E115" t="n">
+        <v>518.61</v>
+      </c>
+      <c r="F115" t="n">
+        <v>142.017300425246</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3316.791856237693</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-538.5539687234498</v>
+      </c>
+      <c r="I115" t="n">
+        <v>6.425</v>
+      </c>
+      <c r="J115" t="n">
+        <v>24.175</v>
+      </c>
+      <c r="K115" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M115" t="n">
+        <v>225.6160617043384</v>
+      </c>
+      <c r="N115" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>352</v>
+      </c>
+      <c r="B116" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" t="n">
+        <v>352</v>
+      </c>
+      <c r="D116" t="n">
+        <v>94.11661713459142</v>
+      </c>
+      <c r="E116" t="n">
+        <v>519.72</v>
+      </c>
+      <c r="F116" t="n">
+        <v>141.7139847870716</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3324.406267979006</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-538.5303396009535</v>
+      </c>
+      <c r="I116" t="n">
+        <v>6.505</v>
+      </c>
+      <c r="J116" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3.855</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5.385</v>
+      </c>
+      <c r="M116" t="n">
+        <v>225.6126808412702</v>
+      </c>
+      <c r="N116" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>352</v>
+      </c>
+      <c r="B117" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" t="n">
+        <v>352</v>
+      </c>
+      <c r="D117" t="n">
+        <v>94.11661713459142</v>
+      </c>
+      <c r="E117" t="n">
+        <v>519.72</v>
+      </c>
+      <c r="F117" t="n">
+        <v>141.7139847870716</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3324.406267979006</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-538.5303396009535</v>
+      </c>
+      <c r="I117" t="n">
+        <v>6.505</v>
+      </c>
+      <c r="J117" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3.855</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5.385</v>
+      </c>
+      <c r="M117" t="n">
+        <v>225.6126808412702</v>
+      </c>
+      <c r="N117" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>352</v>
+      </c>
+      <c r="B118" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" t="n">
+        <v>352</v>
+      </c>
+      <c r="D118" t="n">
+        <v>94.10556376679951</v>
+      </c>
+      <c r="E118" t="n">
+        <v>522.265</v>
+      </c>
+      <c r="F118" t="n">
+        <v>141.0234118187833</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3351.287122179033</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-530.5269374141529</v>
+      </c>
+      <c r="I118" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="J118" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3.965</v>
+      </c>
+      <c r="L118" t="n">
+        <v>5.525</v>
+      </c>
+      <c r="M118" t="n">
+        <v>225.6016400327011</v>
+      </c>
+      <c r="N118" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>352</v>
+      </c>
+      <c r="B119" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" t="n">
+        <v>352</v>
+      </c>
+      <c r="D119" t="n">
+        <v>94.10556376679951</v>
+      </c>
+      <c r="E119" t="n">
+        <v>522.265</v>
+      </c>
+      <c r="F119" t="n">
+        <v>141.0234118187833</v>
+      </c>
+      <c r="G119" t="n">
+        <v>3351.287122179033</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-530.5269374141529</v>
+      </c>
+      <c r="I119" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="J119" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3.965</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.525</v>
+      </c>
+      <c r="M119" t="n">
+        <v>225.6016400327011</v>
+      </c>
+      <c r="N119" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>352</v>
+      </c>
+      <c r="B120" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" t="n">
+        <v>352</v>
+      </c>
+      <c r="D120" t="n">
+        <v>94.10654053093099</v>
+      </c>
+      <c r="E120" t="n">
+        <v>521.3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>141.2844660915727</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3345.744941268133</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-528.0504012925577</v>
+      </c>
+      <c r="I120" t="n">
+        <v>6.675</v>
+      </c>
+      <c r="J120" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="K120" t="n">
+        <v>4.065</v>
+      </c>
+      <c r="L120" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="M120" t="n">
+        <v>225.5966642460446</v>
+      </c>
+      <c r="N120" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>352</v>
+      </c>
+      <c r="B121" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" t="n">
+        <v>352</v>
+      </c>
+      <c r="D121" t="n">
+        <v>94.10654053093099</v>
+      </c>
+      <c r="E121" t="n">
+        <v>521.3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>141.2844660915727</v>
+      </c>
+      <c r="G121" t="n">
+        <v>3345.744941268133</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-528.0504012925577</v>
+      </c>
+      <c r="I121" t="n">
+        <v>6.675</v>
+      </c>
+      <c r="J121" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="K121" t="n">
+        <v>4.065</v>
+      </c>
+      <c r="L121" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="M121" t="n">
+        <v>225.5966642460446</v>
+      </c>
+      <c r="N121" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>352</v>
+      </c>
+      <c r="B122" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" t="n">
+        <v>352</v>
+      </c>
+      <c r="D122" t="n">
+        <v>94.12564539730378</v>
+      </c>
+      <c r="E122" t="n">
+        <v>517.0550000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>142.4444056696809</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3300.041412367954</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-542.648853379734</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J122" t="n">
+        <v>24.645</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L122" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="M122" t="n">
+        <v>225.6170595549788</v>
+      </c>
+      <c r="N122" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>352</v>
+      </c>
+      <c r="B123" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" t="n">
+        <v>352</v>
+      </c>
+      <c r="D123" t="n">
+        <v>94.12564539730378</v>
+      </c>
+      <c r="E123" t="n">
+        <v>517.0550000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>142.4444056696809</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3300.041412367954</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-542.648853379734</v>
+      </c>
+      <c r="I123" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J123" t="n">
+        <v>24.645</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L123" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="M123" t="n">
+        <v>225.6170595549788</v>
+      </c>
+      <c r="N123" t="n">
+        <v>5.154784471845812</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>352</v>
+      </c>
+      <c r="B124" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" t="n">
+        <v>352</v>
+      </c>
+      <c r="D124" t="n">
+        <v>94.11322555079249</v>
+      </c>
+      <c r="E124" t="n">
+        <v>520.98</v>
+      </c>
+      <c r="F124" t="n">
+        <v>141.3712468300834</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3334.384777980824</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-537.8139934184896</v>
+      </c>
+      <c r="I124" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="J124" t="n">
+        <v>25.265</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="L124" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="M124" t="n">
+        <v>225.6135502135314</v>
+      </c>
+      <c r="N124" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>352</v>
+      </c>
+      <c r="B125" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" t="n">
+        <v>352</v>
+      </c>
+      <c r="D125" t="n">
+        <v>94.11322555079249</v>
+      </c>
+      <c r="E125" t="n">
+        <v>520.98</v>
+      </c>
+      <c r="F125" t="n">
+        <v>141.3712468300834</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3334.384777980824</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-537.8139934184896</v>
+      </c>
+      <c r="I125" t="n">
+        <v>6.785</v>
+      </c>
+      <c r="J125" t="n">
+        <v>25.265</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="L125" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="M125" t="n">
+        <v>225.6135502135314</v>
+      </c>
+      <c r="N125" t="n">
+        <v>5.155700279641803</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>352</v>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="n">
+        <v>352</v>
+      </c>
+      <c r="D126" t="n">
+        <v>94.10790644149955</v>
+      </c>
+      <c r="E126" t="n">
+        <v>522.0700000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>141.0760859147947</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3346.61176939004</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-533.2481273065886</v>
+      </c>
+      <c r="I126" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J126" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L126" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>225.6051854309489</v>
+      </c>
+      <c r="N126" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>352</v>
+      </c>
+      <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="n">
+        <v>352</v>
+      </c>
+      <c r="D127" t="n">
+        <v>94.10790644149955</v>
+      </c>
+      <c r="E127" t="n">
+        <v>522.0700000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>141.0760859147947</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3346.61176939004</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-533.2481273065886</v>
+      </c>
+      <c r="I127" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J127" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>5.699999999999999</v>
+      </c>
+      <c r="M127" t="n">
+        <v>225.6051854309489</v>
+      </c>
+      <c r="N127" t="n">
+        <v>5.156460218858072</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>352</v>
+      </c>
+      <c r="B128" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" t="n">
+        <v>352</v>
+      </c>
+      <c r="D128" t="n">
+        <v>94.10088443106447</v>
+      </c>
+      <c r="E128" t="n">
+        <v>523.9400000000001</v>
+      </c>
+      <c r="F128" t="n">
+        <v>140.5725697093882</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3364.437735979728</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-528.9150640810926</v>
+      </c>
+      <c r="I128" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J128" t="n">
+        <v>26.505</v>
+      </c>
+      <c r="K128" t="n">
+        <v>4.149999999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>5.834999999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>225.5975907637723</v>
+      </c>
+      <c r="N128" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>352</v>
+      </c>
+      <c r="B129" t="n">
+        <v>128</v>
+      </c>
+      <c r="C129" t="n">
+        <v>352</v>
+      </c>
+      <c r="D129" t="n">
+        <v>94.10088443106447</v>
+      </c>
+      <c r="E129" t="n">
+        <v>523.9400000000001</v>
+      </c>
+      <c r="F129" t="n">
+        <v>140.5725697093882</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3364.437735979728</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-528.9150640810926</v>
+      </c>
+      <c r="I129" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J129" t="n">
+        <v>26.505</v>
+      </c>
+      <c r="K129" t="n">
+        <v>4.149999999999999</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5.834999999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>225.5975907637723</v>
+      </c>
+      <c r="N129" t="n">
+        <v>5.157092098140571</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>352</v>
+      </c>
+      <c r="B130" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" t="n">
+        <v>352</v>
+      </c>
+      <c r="D130" t="n">
+        <v>94.1489788436523</v>
+      </c>
+      <c r="E130" t="n">
+        <v>500.715</v>
+      </c>
+      <c r="F130" t="n">
+        <v>147.0928415836092</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3325.679734063873</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-642.8930582990762</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5.795</v>
+      </c>
+      <c r="J130" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4.539999999999999</v>
+      </c>
+      <c r="M130" t="n">
+        <v>258.5393249871184</v>
+      </c>
+      <c r="N130" t="n">
+        <v>5.163219248428367</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>352</v>
+      </c>
+      <c r="B131" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" t="n">
+        <v>352</v>
+      </c>
+      <c r="D131" t="n">
+        <v>94.1489788436523</v>
+      </c>
+      <c r="E131" t="n">
+        <v>500.715</v>
+      </c>
+      <c r="F131" t="n">
+        <v>147.0928415836092</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3325.679734063873</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-642.8930582990762</v>
+      </c>
+      <c r="I131" t="n">
+        <v>5.795</v>
+      </c>
+      <c r="J131" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.539999999999999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>258.5393249871184</v>
+      </c>
+      <c r="N131" t="n">
+        <v>5.163219248428367</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>352</v>
+      </c>
+      <c r="B132" t="n">
+        <v>131</v>
+      </c>
+      <c r="C132" t="n">
+        <v>352</v>
+      </c>
+      <c r="D132" t="n">
+        <v>94.13835341204899</v>
+      </c>
+      <c r="E132" t="n">
+        <v>502.88</v>
+      </c>
+      <c r="F132" t="n">
+        <v>146.4595771825025</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3351.168960031674</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-634.8453511645325</v>
+      </c>
+      <c r="I132" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="J132" t="n">
+        <v>22.155</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M132" t="n">
+        <v>258.3560892061806</v>
+      </c>
+      <c r="N132" t="n">
+        <v>5.165048411396795</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>352</v>
+      </c>
+      <c r="B133" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" t="n">
+        <v>352</v>
+      </c>
+      <c r="D133" t="n">
+        <v>94.13835341204899</v>
+      </c>
+      <c r="E133" t="n">
+        <v>502.88</v>
+      </c>
+      <c r="F133" t="n">
+        <v>146.4595771825025</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3351.168960031674</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-634.8453511645325</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5.895</v>
+      </c>
+      <c r="J133" t="n">
+        <v>22.155</v>
+      </c>
+      <c r="K133" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L133" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="M133" t="n">
+        <v>258.3560892061806</v>
+      </c>
+      <c r="N133" t="n">
+        <v>5.165048411396795</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>352</v>
+      </c>
+      <c r="B134" t="n">
+        <v>133</v>
+      </c>
+      <c r="C134" t="n">
+        <v>352</v>
+      </c>
+      <c r="D134" t="n">
+        <v>94.12901458157525</v>
+      </c>
+      <c r="E134" t="n">
+        <v>504.455</v>
+      </c>
+      <c r="F134" t="n">
+        <v>146.0023038200372</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3371.975091966616</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-626.169256577645</v>
+      </c>
+      <c r="I134" t="n">
+        <v>6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>22.735</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="M134" t="n">
+        <v>258.1716552746464</v>
+      </c>
+      <c r="N134" t="n">
+        <v>5.166663614743454</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>352</v>
+      </c>
+      <c r="B135" t="n">
+        <v>134</v>
+      </c>
+      <c r="C135" t="n">
+        <v>352</v>
+      </c>
+      <c r="D135" t="n">
+        <v>94.12901458157525</v>
+      </c>
+      <c r="E135" t="n">
+        <v>504.455</v>
+      </c>
+      <c r="F135" t="n">
+        <v>146.0023038200372</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3371.975091966616</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-626.169256577645</v>
+      </c>
+      <c r="I135" t="n">
+        <v>6</v>
+      </c>
+      <c r="J135" t="n">
+        <v>22.735</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="L135" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="M135" t="n">
+        <v>258.1716552746464</v>
+      </c>
+      <c r="N135" t="n">
+        <v>5.166663614743454</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>352</v>
+      </c>
+      <c r="B136" t="n">
+        <v>135</v>
+      </c>
+      <c r="C136" t="n">
+        <v>352</v>
+      </c>
+      <c r="D136" t="n">
+        <v>94.11988251248498</v>
+      </c>
+      <c r="E136" t="n">
+        <v>506.615</v>
+      </c>
+      <c r="F136" t="n">
+        <v>145.3798094678145</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3394.921801047421</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-620.2983737205636</v>
+      </c>
+      <c r="I136" t="n">
+        <v>6.105</v>
+      </c>
+      <c r="J136" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3.624999999999999</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M136" t="n">
+        <v>257.9860097846073</v>
+      </c>
+      <c r="N136" t="n">
+        <v>5.167857766649748</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>352</v>
+      </c>
+      <c r="B137" t="n">
+        <v>136</v>
+      </c>
+      <c r="C137" t="n">
+        <v>352</v>
+      </c>
+      <c r="D137" t="n">
+        <v>94.11988251248498</v>
+      </c>
+      <c r="E137" t="n">
+        <v>506.615</v>
+      </c>
+      <c r="F137" t="n">
+        <v>145.3798094678145</v>
+      </c>
+      <c r="G137" t="n">
+        <v>3394.921801047421</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-620.2983737205636</v>
+      </c>
+      <c r="I137" t="n">
+        <v>6.105</v>
+      </c>
+      <c r="J137" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="K137" t="n">
+        <v>3.624999999999999</v>
+      </c>
+      <c r="L137" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M137" t="n">
+        <v>257.9860097846073</v>
+      </c>
+      <c r="N137" t="n">
+        <v>5.167857766649748</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>352</v>
+      </c>
+      <c r="B138" t="n">
+        <v>137</v>
+      </c>
+      <c r="C138" t="n">
+        <v>352</v>
+      </c>
+      <c r="D138" t="n">
+        <v>94.12929414434481</v>
+      </c>
+      <c r="E138" t="n">
+        <v>503.875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>146.1703640258732</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3369.31150234771</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-624.3822320454065</v>
+      </c>
+      <c r="I138" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="J138" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="K138" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L138" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="M138" t="n">
+        <v>225.6785786607889</v>
+      </c>
+      <c r="N138" t="n">
+        <v>5.155945085363528</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>352</v>
+      </c>
+      <c r="B139" t="n">
+        <v>138</v>
+      </c>
+      <c r="C139" t="n">
+        <v>352</v>
+      </c>
+      <c r="D139" t="n">
+        <v>94.12929414434481</v>
+      </c>
+      <c r="E139" t="n">
+        <v>503.875</v>
+      </c>
+      <c r="F139" t="n">
+        <v>146.1703640258732</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3369.31150234771</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-624.3822320454065</v>
+      </c>
+      <c r="I139" t="n">
+        <v>5.985</v>
+      </c>
+      <c r="J139" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L139" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="M139" t="n">
+        <v>225.6785786607889</v>
+      </c>
+      <c r="N139" t="n">
+        <v>5.155945085363528</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>352</v>
+      </c>
+      <c r="B140" t="n">
+        <v>139</v>
+      </c>
+      <c r="C140" t="n">
+        <v>352</v>
+      </c>
+      <c r="D140" t="n">
+        <v>94.1176800740742</v>
+      </c>
+      <c r="E140" t="n">
+        <v>505.99</v>
+      </c>
+      <c r="F140" t="n">
+        <v>145.559382939459</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3396.198718014977</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-614.6089804700042</v>
+      </c>
+      <c r="I140" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="J140" t="n">
+        <v>22.515</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L140" t="n">
+        <v>4.890000000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>225.6677542230229</v>
+      </c>
+      <c r="N140" t="n">
+        <v>5.156939034068073</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>352</v>
+      </c>
+      <c r="B141" t="n">
+        <v>140</v>
+      </c>
+      <c r="C141" t="n">
+        <v>352</v>
+      </c>
+      <c r="D141" t="n">
+        <v>94.1176800740742</v>
+      </c>
+      <c r="E141" t="n">
+        <v>505.99</v>
+      </c>
+      <c r="F141" t="n">
+        <v>145.559382939459</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3396.198718014977</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-614.6089804700042</v>
+      </c>
+      <c r="I141" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="J141" t="n">
+        <v>22.515</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L141" t="n">
+        <v>4.890000000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>225.6677542230229</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5.156939034068073</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>352</v>
+      </c>
+      <c r="B142" t="n">
+        <v>141</v>
+      </c>
+      <c r="C142" t="n">
+        <v>352</v>
+      </c>
+      <c r="D142" t="n">
+        <v>94.10879247890132</v>
+      </c>
+      <c r="E142" t="n">
+        <v>507.7</v>
+      </c>
+      <c r="F142" t="n">
+        <v>145.0691199006044</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3416.993644330058</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-607.3514750394983</v>
+      </c>
+      <c r="I142" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="J142" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="K142" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="L142" t="n">
+        <v>5.015000000000001</v>
+      </c>
+      <c r="M142" t="n">
+        <v>225.657973057641</v>
+      </c>
+      <c r="N142" t="n">
+        <v>5.15778066693646</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>352</v>
+      </c>
+      <c r="B143" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" t="n">
+        <v>352</v>
+      </c>
+      <c r="D143" t="n">
+        <v>94.10879247890132</v>
+      </c>
+      <c r="E143" t="n">
+        <v>507.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>145.0691199006044</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3416.993644330058</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-607.3514750394983</v>
+      </c>
+      <c r="I143" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="J143" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="L143" t="n">
+        <v>5.015000000000001</v>
+      </c>
+      <c r="M143" t="n">
+        <v>225.657973057641</v>
+      </c>
+      <c r="N143" t="n">
+        <v>5.15778066693646</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>352</v>
+      </c>
+      <c r="B144" t="n">
+        <v>143</v>
+      </c>
+      <c r="C144" t="n">
+        <v>352</v>
+      </c>
+      <c r="D144" t="n">
+        <v>94.09990610388661</v>
+      </c>
+      <c r="E144" t="n">
+        <v>509.595</v>
+      </c>
+      <c r="F144" t="n">
+        <v>144.5296601684413</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3438.380081732805</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-600.6945780404083</v>
+      </c>
+      <c r="I144" t="n">
+        <v>6.205</v>
+      </c>
+      <c r="J144" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="M144" t="n">
+        <v>225.6482751433331</v>
+      </c>
+      <c r="N144" t="n">
+        <v>5.15849600975352</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>352</v>
+      </c>
+      <c r="B145" t="n">
+        <v>144</v>
+      </c>
+      <c r="C145" t="n">
+        <v>352</v>
+      </c>
+      <c r="D145" t="n">
+        <v>94.09990610388661</v>
+      </c>
+      <c r="E145" t="n">
+        <v>509.595</v>
+      </c>
+      <c r="F145" t="n">
+        <v>144.5296601684413</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3438.380081732805</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-600.6945780404083</v>
+      </c>
+      <c r="I145" t="n">
+        <v>6.205</v>
+      </c>
+      <c r="J145" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="K145" t="n">
+        <v>3.715</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="M145" t="n">
+        <v>225.6482751433331</v>
+      </c>
+      <c r="N145" t="n">
+        <v>5.15849600975352</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>352</v>
+      </c>
+      <c r="B146" t="n">
+        <v>145</v>
+      </c>
+      <c r="C146" t="n">
+        <v>352</v>
+      </c>
+      <c r="D146" t="n">
+        <v>94.08995949812969</v>
+      </c>
+      <c r="E146" t="n">
+        <v>512.485</v>
+      </c>
+      <c r="F146" t="n">
+        <v>143.7146300350973</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3466.355251007948</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-597.3041552616934</v>
+      </c>
+      <c r="I146" t="n">
+        <v>6.255</v>
+      </c>
+      <c r="J146" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="K146" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L146" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="M146" t="n">
+        <v>225.6719931441504</v>
+      </c>
+      <c r="N146" t="n">
+        <v>5.154158664022789</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>352</v>
+      </c>
+      <c r="B147" t="n">
+        <v>146</v>
+      </c>
+      <c r="C147" t="n">
+        <v>352</v>
+      </c>
+      <c r="D147" t="n">
+        <v>94.08995949812969</v>
+      </c>
+      <c r="E147" t="n">
+        <v>512.485</v>
+      </c>
+      <c r="F147" t="n">
+        <v>143.7146300350973</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3466.355251007948</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-597.3041552616934</v>
+      </c>
+      <c r="I147" t="n">
+        <v>6.255</v>
+      </c>
+      <c r="J147" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="L147" t="n">
+        <v>4.960000000000001</v>
+      </c>
+      <c r="M147" t="n">
+        <v>225.6719931441504</v>
+      </c>
+      <c r="N147" t="n">
+        <v>5.154158664022789</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>352</v>
+      </c>
+      <c r="B148" t="n">
+        <v>147</v>
+      </c>
+      <c r="C148" t="n">
+        <v>352</v>
+      </c>
+      <c r="D148" t="n">
+        <v>94.08354351692012</v>
+      </c>
+      <c r="E148" t="n">
+        <v>514.325</v>
+      </c>
+      <c r="F148" t="n">
+        <v>143.2004902999793</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3483.571310129491</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-594.2804842044536</v>
+      </c>
+      <c r="I148" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="J148" t="n">
+        <v>23</v>
+      </c>
+      <c r="K148" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5.079999999999999</v>
+      </c>
+      <c r="M148" t="n">
+        <v>225.6640756636884</v>
+      </c>
+      <c r="N148" t="n">
+        <v>5.155033593899832</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>352</v>
+      </c>
+      <c r="B149" t="n">
+        <v>148</v>
+      </c>
+      <c r="C149" t="n">
+        <v>352</v>
+      </c>
+      <c r="D149" t="n">
+        <v>94.08354351692012</v>
+      </c>
+      <c r="E149" t="n">
+        <v>514.325</v>
+      </c>
+      <c r="F149" t="n">
+        <v>143.2004902999793</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3483.571310129491</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-594.2804842044536</v>
+      </c>
+      <c r="I149" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="J149" t="n">
+        <v>23</v>
+      </c>
+      <c r="K149" t="n">
+        <v>3.609999999999999</v>
+      </c>
+      <c r="L149" t="n">
+        <v>5.079999999999999</v>
+      </c>
+      <c r="M149" t="n">
+        <v>225.6640756636884</v>
+      </c>
+      <c r="N149" t="n">
+        <v>5.155033593899832</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>352</v>
+      </c>
+      <c r="B150" t="n">
+        <v>149</v>
+      </c>
+      <c r="C150" t="n">
+        <v>352</v>
+      </c>
+      <c r="D150" t="n">
+        <v>94.07556814531863</v>
+      </c>
+      <c r="E150" t="n">
+        <v>515.76</v>
+      </c>
+      <c r="F150" t="n">
+        <v>142.8020633114954</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3501.787771490186</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-587.3230833165272</v>
+      </c>
+      <c r="I150" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="J150" t="n">
+        <v>23.555</v>
+      </c>
+      <c r="K150" t="n">
+        <v>3.704999999999999</v>
+      </c>
+      <c r="L150" t="n">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="M150" t="n">
+        <v>225.6634424020232</v>
+      </c>
+      <c r="N150" t="n">
+        <v>5.155750754655417</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>352</v>
+      </c>
+      <c r="B151" t="n">
+        <v>150</v>
+      </c>
+      <c r="C151" t="n">
+        <v>352</v>
+      </c>
+      <c r="D151" t="n">
+        <v>94.07556814531863</v>
+      </c>
+      <c r="E151" t="n">
+        <v>515.76</v>
+      </c>
+      <c r="F151" t="n">
+        <v>142.8020633114954</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3501.787771490186</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-587.3230833165272</v>
+      </c>
+      <c r="I151" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="J151" t="n">
+        <v>23.555</v>
+      </c>
+      <c r="K151" t="n">
+        <v>3.704999999999999</v>
+      </c>
+      <c r="L151" t="n">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="M151" t="n">
+        <v>225.6634424020232</v>
+      </c>
+      <c r="N151" t="n">
+        <v>5.155750754655417</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>352</v>
+      </c>
+      <c r="B152" t="n">
+        <v>151</v>
+      </c>
+      <c r="C152" t="n">
+        <v>352</v>
+      </c>
+      <c r="D152" t="n">
+        <v>94.06518569885561</v>
+      </c>
+      <c r="E152" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="F152" t="n">
+        <v>142.2119949286288</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3526.580361416173</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-579.3527473916239</v>
+      </c>
+      <c r="I152" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="J152" t="n">
+        <v>24.115</v>
+      </c>
+      <c r="K152" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L152" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="M152" t="n">
+        <v>225.647870471401</v>
+      </c>
+      <c r="N152" t="n">
+        <v>5.156338897276304</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>352</v>
+      </c>
+      <c r="B153" t="n">
+        <v>152</v>
+      </c>
+      <c r="C153" t="n">
+        <v>352</v>
+      </c>
+      <c r="D153" t="n">
+        <v>94.06518569885561</v>
+      </c>
+      <c r="E153" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="F153" t="n">
+        <v>142.2119949286288</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3526.580361416173</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-579.3527473916239</v>
+      </c>
+      <c r="I153" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="J153" t="n">
+        <v>24.115</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L153" t="n">
+        <v>5.325</v>
+      </c>
+      <c r="M153" t="n">
+        <v>225.647870471401</v>
+      </c>
+      <c r="N153" t="n">
+        <v>5.156338897276304</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>352</v>
+      </c>
+      <c r="B154" t="n">
+        <v>153</v>
+      </c>
+      <c r="C154" t="n">
+        <v>352</v>
+      </c>
+      <c r="D154" t="n">
+        <v>94.08960372476547</v>
+      </c>
+      <c r="E154" t="n">
+        <v>512.48</v>
+      </c>
+      <c r="F154" t="n">
+        <v>143.7160321837669</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3466.724674474564</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-596.5463447656517</v>
+      </c>
+      <c r="I154" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="J154" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="L154" t="n">
+        <v>5.140000000000001</v>
+      </c>
+      <c r="M154" t="n">
+        <v>225.6724038487482</v>
+      </c>
+      <c r="N154" t="n">
+        <v>5.154158664022789</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>352</v>
+      </c>
+      <c r="B155" t="n">
+        <v>154</v>
+      </c>
+      <c r="C155" t="n">
+        <v>352</v>
+      </c>
+      <c r="D155" t="n">
+        <v>94.08960372476547</v>
+      </c>
+      <c r="E155" t="n">
+        <v>512.48</v>
+      </c>
+      <c r="F155" t="n">
+        <v>143.7160321837669</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3466.724674474564</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-596.5463447656517</v>
+      </c>
+      <c r="I155" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="J155" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="K155" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="L155" t="n">
+        <v>5.140000000000001</v>
+      </c>
+      <c r="M155" t="n">
+        <v>225.6724038487482</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5.154158664022789</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>352</v>
+      </c>
+      <c r="B156" t="n">
+        <v>155</v>
+      </c>
+      <c r="C156" t="n">
+        <v>352</v>
+      </c>
+      <c r="D156" t="n">
+        <v>94.08510900405766</v>
+      </c>
+      <c r="E156" t="n">
+        <v>512.5700000000001</v>
+      </c>
+      <c r="F156" t="n">
+        <v>143.69079769307</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3473.801150791409</v>
+      </c>
+      <c r="H156" t="n">
+        <v>-589.4195439172278</v>
+      </c>
+      <c r="I156" t="n">
+        <v>6.605</v>
+      </c>
+      <c r="J156" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="K156" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5.265</v>
+      </c>
+      <c r="M156" t="n">
+        <v>225.6693801460776</v>
+      </c>
+      <c r="N156" t="n">
+        <v>5.155033593899832</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>352</v>
+      </c>
+      <c r="B157" t="n">
         <v>156</v>
       </c>
-      <c r="C13" t="n">
-        <v>352</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C157" t="n">
+        <v>352</v>
+      </c>
+      <c r="D157" t="n">
         <v>94.08510900405766</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E157" t="n">
         <v>512.5700000000001</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F157" t="n">
         <v>143.69079769307</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G157" t="n">
         <v>3473.801150791409</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H157" t="n">
         <v>-589.4195439172278</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I157" t="n">
         <v>6.605</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J157" t="n">
         <v>23.47</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K157" t="n">
         <v>3.705</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L157" t="n">
         <v>5.265</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M157" t="n">
         <v>225.6693801460776</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N157" t="n">
         <v>5.155033593899832</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>352</v>
+      </c>
+      <c r="B158" t="n">
+        <v>157</v>
+      </c>
+      <c r="C158" t="n">
+        <v>352</v>
+      </c>
+      <c r="D158" t="n">
+        <v>94.07428507554467</v>
+      </c>
+      <c r="E158" t="n">
+        <v>515.415</v>
+      </c>
+      <c r="F158" t="n">
+        <v>142.8976498036279</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3502.215284484501</v>
+      </c>
+      <c r="H158" t="n">
+        <v>-583.6873328990716</v>
+      </c>
+      <c r="I158" t="n">
+        <v>6.685</v>
+      </c>
+      <c r="J158" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="K158" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L158" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M158" t="n">
+        <v>225.6615521767813</v>
+      </c>
+      <c r="N158" t="n">
+        <v>5.155750754655417</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>352</v>
+      </c>
+      <c r="B159" t="n">
+        <v>158</v>
+      </c>
+      <c r="C159" t="n">
+        <v>352</v>
+      </c>
+      <c r="D159" t="n">
+        <v>94.07428507554467</v>
+      </c>
+      <c r="E159" t="n">
+        <v>515.415</v>
+      </c>
+      <c r="F159" t="n">
+        <v>142.8976498036279</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3502.215284484501</v>
+      </c>
+      <c r="H159" t="n">
+        <v>-583.6873328990716</v>
+      </c>
+      <c r="I159" t="n">
+        <v>6.685</v>
+      </c>
+      <c r="J159" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="K159" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L159" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M159" t="n">
+        <v>225.6615521767813</v>
+      </c>
+      <c r="N159" t="n">
+        <v>5.155750754655417</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>352</v>
+      </c>
+      <c r="B160" t="n">
+        <v>159</v>
+      </c>
+      <c r="C160" t="n">
+        <v>352</v>
+      </c>
+      <c r="D160" t="n">
+        <v>94.06789705757966</v>
+      </c>
+      <c r="E160" t="n">
+        <v>517.625</v>
+      </c>
+      <c r="F160" t="n">
+        <v>142.2875482705373</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3520.799420206426</v>
+      </c>
+      <c r="H160" t="n">
+        <v>-582.127402984613</v>
+      </c>
+      <c r="I160" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="J160" t="n">
+        <v>24.595</v>
+      </c>
+      <c r="K160" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="L160" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M160" t="n">
+        <v>225.6507693000977</v>
+      </c>
+      <c r="N160" t="n">
+        <v>5.156338897276304</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>352</v>
+      </c>
+      <c r="B161" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" t="n">
+        <v>352</v>
+      </c>
+      <c r="D161" t="n">
+        <v>94.06789705757966</v>
+      </c>
+      <c r="E161" t="n">
+        <v>517.625</v>
+      </c>
+      <c r="F161" t="n">
+        <v>142.2875482705373</v>
+      </c>
+      <c r="G161" t="n">
+        <v>3520.799420206426</v>
+      </c>
+      <c r="H161" t="n">
+        <v>-582.127402984613</v>
+      </c>
+      <c r="I161" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="J161" t="n">
+        <v>24.595</v>
+      </c>
+      <c r="K161" t="n">
+        <v>3.895</v>
+      </c>
+      <c r="L161" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="M161" t="n">
+        <v>225.6507693000977</v>
+      </c>
+      <c r="N161" t="n">
+        <v>5.156338897276304</v>
       </c>
     </row>
   </sheetData>
